--- a/data/input/preparation/ai_results/quality_reports/puma_disagreements_Information_valence_human.xlsx
+++ b/data/input/preparation/ai_results/quality_reports/puma_disagreements_Information_valence_human.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -483,27 +483,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DEU20P00-04</t>
+          <t>DEU20P00-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CHALL</t>
+          <t>STAKE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CHALL</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEU20P00-10</t>
+          <t>DEU21P00-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -547,12 +547,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEU20P00-12</t>
+          <t>DEU21P00-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>STAKE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>CHALL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -579,27 +579,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEU20P00-18</t>
+          <t>DEU22P00-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -611,27 +611,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEU21P00-07</t>
+          <t>DEU22P00-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CHALL</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DEU21P00-11</t>
+          <t>DEU25P00-00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>STAKE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -675,12 +675,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DEU21P00-12</t>
+          <t>DEU25P00-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>STRAT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>STAKE</t>
+          <t>STRAT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -707,12 +707,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DEU21P00-14</t>
+          <t>DEU25P00-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>STRAT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -722,399 +722,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CHALL</t>
+          <t>STRAT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DEU22P00-10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PERF</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DEU22P00-12</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DEU22P00-18</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DEU23P00-09</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PEOPLE</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PEOPLE</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DEU23P00-10</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PERF</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CHALL</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>DEU23P00-22</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>STAKE</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DEU24P00-02</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PERF</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>negative</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>PERF</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>DEU25P00-00</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>STAKE</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DEU25P00-05</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>DEU25P00-07</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>STRAT</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>STRAT</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>DEU25P00-10</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>STRAT</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>STRAT</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>puma</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DEU25P00-15</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>STAKE</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
         <is>
           <t>puma</t>
         </is>
